--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Downtown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Downtown_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Container - Soup (16oz)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5.22</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>5.22</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.22</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Celsius - Vibe Peach, Tropical, Arctic</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>28.49</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>28.49</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="E3" t="n">
+        <v>28.49</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Chobani - Drinkable Yogurt</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>17.99</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>17.99</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17.99</v>
       </c>
     </row>
     <row r="5">
@@ -531,20 +513,14 @@
           <t>Employee Water</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>8.79</t>
-        </is>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +530,14 @@
           <t>Essentia Water</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="7">
@@ -577,20 +547,14 @@
           <t>Evian 1L</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -600,20 +564,14 @@
           <t>Fiji Water 1L</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>33.00</t>
-        </is>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -627,20 +585,14 @@
           <t>Maple Syrup (pure)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>42</v>
+      </c>
+      <c r="E9" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -650,20 +602,14 @@
           <t>Red Bull</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>85.70</t>
-        </is>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="E10" t="n">
+        <v>85.7</v>
       </c>
     </row>
     <row r="11">
@@ -677,20 +623,14 @@
           <t>Smoked Salmon (Sliced)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>85.85</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>257.55</t>
-        </is>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>257.55</v>
       </c>
     </row>
     <row r="12">
@@ -704,20 +644,14 @@
           <t>Vita Coco - Coconut Water 1L</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>47.00</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>47.00</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>47</v>
+      </c>
+      <c r="E12" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -731,20 +665,14 @@
           <t>Vita Coco - Coconut Water 500ml</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>23.93</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>23.93</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="E13" t="n">
+        <v>23.93</v>
       </c>
     </row>
     <row r="14">
@@ -754,20 +682,14 @@
           <t>Bag - Wax (Sandwich)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>21.01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>21.01</t>
-        </is>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="E14" t="n">
+        <v>21.01</v>
       </c>
     </row>
     <row r="15">
@@ -777,20 +699,14 @@
           <t>Capers</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -804,20 +720,14 @@
           <t>Container - Deli (16oz)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.73</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2.73</t>
-        </is>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.73</v>
       </c>
     </row>
     <row r="17">
@@ -827,20 +737,14 @@
           <t>Container - Muffin (1 Pack)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>11.50</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>11.50</t>
-        </is>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11.5</v>
       </c>
     </row>
     <row r="18">
@@ -854,20 +758,14 @@
           <t>Cup - Espresso (4oz)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="19">
@@ -881,20 +779,14 @@
           <t>Cup - Hot (8oz)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -908,20 +800,14 @@
           <t>Cup - Portion (2oz)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.77</v>
       </c>
     </row>
     <row r="21">
@@ -935,20 +821,14 @@
           <t>Cup - Portion (3.25oz)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>5.23</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>5.23</t>
-        </is>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5.23</v>
       </c>
     </row>
     <row r="22">
@@ -958,20 +838,14 @@
           <t>Honey - Jug</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="23">
@@ -985,20 +859,14 @@
           <t>Jam - Strawberry</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1012,20 +880,14 @@
           <t>Kilogram Chai Concentrate</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>86.10</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>86.10</t>
-        </is>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1039,20 +901,14 @@
           <t>Lid - Deli (6/32oz)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.63</v>
       </c>
     </row>
     <row r="26">
@@ -1066,20 +922,14 @@
           <t>Lid Espresso - 4oz</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="27">
@@ -1089,20 +939,14 @@
           <t>Monin - White Chocolate</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1112,20 +956,14 @@
           <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E28" t="n">
+        <v>13.92</v>
       </c>
     </row>
     <row r="29">
@@ -1135,20 +973,14 @@
           <t>Tea Bags - Throat Coat (Traditional Medicinals)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>5.09</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>5.09</t>
-        </is>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5.09</v>
       </c>
     </row>
     <row r="30">
@@ -1162,20 +994,14 @@
           <t>Torani - Dark Chocolate Sauce</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1189,20 +1015,14 @@
           <t>Wrap - Foil (9" x 10.75")</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1216,20 +1036,14 @@
           <t>Wrap - Paper (15" x 10.75")</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>5.97</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>5.97</t>
-        </is>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5.97</v>
       </c>
     </row>
     <row r="33">
@@ -1243,20 +1057,14 @@
           <t>Whitefish Salad</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>77.97</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>77.97</t>
-        </is>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>77.97</v>
+      </c>
+      <c r="E33" t="n">
+        <v>77.97</v>
       </c>
     </row>
     <row r="34">
@@ -1266,20 +1074,14 @@
           <t>Non-Dairy Creamer</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
